--- a/data/trans_orig/P37B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023</t>
+          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023 (tasa de respuesta: 97,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65156</t>
+          <t>67487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35478</t>
+          <t>33528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>36099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84682</t>
+          <t>86069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4326</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>3130</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9977</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>11077</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>10704</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>266526</t>
+          <t>268128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>322007</t>
+          <t>321794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204098</t>
+          <t>201788</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237304</t>
+          <t>235026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>485683</t>
+          <t>486540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>548166</t>
+          <t>549329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51513</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36534</t>
+          <t>36306</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31326</t>
+          <t>30516</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76206</t>
+          <t>71286</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14214</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44559</t>
+          <t>44688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>36694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32668</t>
+          <t>32458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71701</t>
+          <t>70318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,62 +1560,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2165</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>7224</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1292</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>7458</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28691</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>279174</t>
+          <t>279824</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316028</t>
+          <t>316722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>340993</t>
+          <t>343366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>390453</t>
+          <t>391609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>634879</t>
+          <t>637290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>696560</t>
+          <t>697855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36479</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18264</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47107</t>
+          <t>46150</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38817</t>
+          <t>37796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>72961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>29145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55760</t>
+          <t>54423</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>37488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59817</t>
+          <t>60161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71403</t>
+          <t>71239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106110</t>
+          <t>104672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25566</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,82 +2335,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>10660</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17545</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>25664</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>17642</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>37315</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>10660</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6009</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>17261</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>25664</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>17750</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>37183</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>334836</t>
+          <t>336617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>371650</t>
+          <t>370860</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>333386</t>
+          <t>333166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>362288</t>
+          <t>363037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>678688</t>
+          <t>682005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>725935</t>
+          <t>724962</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,98%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40622</t>
+          <t>40122</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29138</t>
+          <t>28206</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47332</t>
+          <t>47393</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53284</t>
+          <t>53153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81596</t>
+          <t>79797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60863</t>
+          <t>61719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>533239</t>
+          <t>548254</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32673</t>
+          <t>32985</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56240</t>
+          <t>56071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101720</t>
+          <t>101577</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>742758</t>
+          <t>763322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56674</t>
+          <t>57466</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40634</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74629</t>
+          <t>72891</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>172760</t>
+          <t>165014</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>582483</t>
+          <t>584137</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>443370</t>
+          <t>443371</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>423120</t>
+          <t>424283</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>463318</t>
+          <t>463771</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>459480</t>
+          <t>454760</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1035284</t>
+          <t>1037307</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67360</t>
+          <t>66742</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>33993</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55179</t>
+          <t>53873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45252</t>
+          <t>47317</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111266</t>
+          <t>109279</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>548074</t>
+          <t>548075</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>548074</t>
+          <t>548075</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>548074</t>
+          <t>548075</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>47422</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49881</t>
+          <t>48954</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60639</t>
+          <t>61787</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>89858</t>
+          <t>90759</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30750</t>
+          <t>30906</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>245275</t>
+          <t>247532</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>276996</t>
+          <t>277530</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>235967</t>
+          <t>237973</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>260988</t>
+          <t>260989</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>490204</t>
+          <t>490587</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>530473</t>
+          <t>529944</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45063</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>21727</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>37382</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>49737</t>
+          <t>50369</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>75693</t>
+          <t>76040</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22259</t>
+          <t>22653</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>17742</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29708</t>
+          <t>29265</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30133</t>
+          <t>30270</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>47391</t>
+          <t>47524</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>55868</t>
+          <t>56966</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>71812</t>
+          <t>72279</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>51153</t>
+          <t>50973</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>64829</t>
+          <t>64972</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>112470</t>
+          <t>112465</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>133306</t>
+          <t>132717</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>22224</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>19612</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>32624</t>
+          <t>31961</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>36216</t>
+          <t>36658</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>225787</t>
+          <t>224683</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>937615</t>
+          <t>1024458</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>181719</t>
+          <t>184339</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>240820</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>433020</t>
+          <t>427884</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1522990</t>
+          <t>1330652</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>29621</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>52446</t>
+          <t>50834</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>105609</t>
+          <t>104547</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>43828</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>79494</t>
+          <t>78916</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,47 +5780,47 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>132178</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>103950</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>166601</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
           <t>3,66%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>132178</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>104605</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>166943</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1251894</t>
+          <t>1187141</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1884026</t>
+          <t>1884601</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1662265</t>
+          <t>1665455</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1759985</t>
+          <t>1756033</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2675225</t>
+          <t>2806577</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3598678</t>
+          <t>3599820</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>114282</t>
+          <t>116058</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>201449</t>
+          <t>201349</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>154141</t>
+          <t>152412</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>203696</t>
+          <t>203517</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>287247</t>
+          <t>284619</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>393770</t>
+          <t>390844</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>37635</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22296</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67487</t>
+          <t>61178</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17653</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>41249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>61753</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36099</t>
+          <t>39572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86069</t>
+          <t>88207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>23171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>299237</t>
+          <t>309114</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>268128</t>
+          <t>281983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>321794</t>
+          <t>330172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>221878</t>
+          <t>255177</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201788</t>
+          <t>235606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>235026</t>
+          <t>272801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>521115</t>
+          <t>564291</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>486540</t>
+          <t>532093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>549329</t>
+          <t>593079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25804</t>
+          <t>23237</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49795</t>
+          <t>41560</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36306</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>47731</t>
+          <t>48177</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30516</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71286</t>
+          <t>71116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>365321</t>
+          <t>376484</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>365321</t>
+          <t>376484</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>365321</t>
+          <t>376484</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>266484</t>
+          <t>309328</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>266484</t>
+          <t>309328</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>266484</t>
+          <t>309328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>631805</t>
+          <t>685812</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>631805</t>
+          <t>685812</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>631805</t>
+          <t>685812</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>30411</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44688</t>
+          <t>47875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36694</t>
+          <t>40516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49692</t>
+          <t>57603</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32458</t>
+          <t>41256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70318</t>
+          <t>79261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>36371</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>299881</t>
+          <t>335134</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>279824</t>
+          <t>314965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316722</t>
+          <t>356184</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>363845</t>
+          <t>334262</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>343366</t>
+          <t>316270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>391609</t>
+          <t>349512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>663725</t>
+          <t>669395</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>637290</t>
+          <t>640161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>697855</t>
+          <t>693358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22545</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36074</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>37937</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46150</t>
+          <t>50643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>54775</t>
+          <t>63408</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37796</t>
+          <t>47553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72961</t>
+          <t>82041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>358933</t>
+          <t>406212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>358933</t>
+          <t>406212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>358933</t>
+          <t>406212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>427497</t>
+          <t>407931</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>427497</t>
+          <t>407931</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>427497</t>
+          <t>407931</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>786430</t>
+          <t>814143</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>786430</t>
+          <t>814143</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>786430</t>
+          <t>814143</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39935</t>
+          <t>48003</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54423</t>
+          <t>64233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>53852</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37488</t>
+          <t>42945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60161</t>
+          <t>67355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>86662</t>
+          <t>101855</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71239</t>
+          <t>84320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104672</t>
+          <t>122910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -2315,27 +2315,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>18351</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>25664</t>
+          <t>31107</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37315</t>
+          <t>44442</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>354848</t>
+          <t>414792</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>336617</t>
+          <t>396174</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>370860</t>
+          <t>433088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>349389</t>
+          <t>403254</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>333166</t>
+          <t>387130</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>363037</t>
+          <t>418025</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>704237</t>
+          <t>818046</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>682005</t>
+          <t>791409</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>724962</t>
+          <t>842214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>28709</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>23080</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40122</t>
+          <t>45008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>37195</t>
+          <t>41637</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28206</t>
+          <t>32085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47393</t>
+          <t>52728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>65904</t>
+          <t>74577</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53153</t>
+          <t>59535</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79797</t>
+          <t>90594</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>438660</t>
+          <t>515297</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>438660</t>
+          <t>515297</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>438660</t>
+          <t>515297</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>445636</t>
+          <t>513743</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>445636</t>
+          <t>513743</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>445636</t>
+          <t>513743</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>884296</t>
+          <t>1029040</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>884296</t>
+          <t>1029040</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>884296</t>
+          <t>1029040</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>290641</t>
+          <t>52863</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61719</t>
+          <t>38023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>548254</t>
+          <t>71677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43632</t>
+          <t>49314</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32985</t>
+          <t>39686</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56071</t>
+          <t>61323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>334273</t>
+          <t>102177</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101577</t>
+          <t>83531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>763322</t>
+          <t>121859</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>864</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>24803</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57466</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>40217</t>
+          <t>35395</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72891</t>
+          <t>47829</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>385481</t>
+          <t>423189</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>165014</t>
+          <t>399949</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>584137</t>
+          <t>442074</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>443371</t>
+          <t>448921</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>424283</t>
+          <t>433851</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>463771</t>
+          <t>464259</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>828851</t>
+          <t>872109</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>454760</t>
+          <t>841916</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1037307</t>
+          <t>896157</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>40536</t>
+          <t>42516</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>31830</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66742</t>
+          <t>56078</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>47089</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33993</t>
+          <t>37165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53873</t>
+          <t>57417</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>84372</t>
+          <t>89605</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47317</t>
+          <t>74428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>109279</t>
+          <t>107724</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>743827</t>
+          <t>544235</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>743827</t>
+          <t>544235</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>743827</t>
+          <t>544235</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>548075</t>
+          <t>559401</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>548075</t>
+          <t>559401</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>548075</t>
+          <t>559401</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1291901</t>
+          <t>1103635</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1291901</t>
+          <t>1103635</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1291901</t>
+          <t>1103635</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>37178</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>26626</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47422</t>
+          <t>49371</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>43362</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>34731</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48954</t>
+          <t>52890</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>74887</t>
+          <t>80540</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61787</t>
+          <t>66491</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>90759</t>
+          <t>96083</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10761</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>36252</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>262481</t>
+          <t>287542</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>247532</t>
+          <t>269924</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>277530</t>
+          <t>302384</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>249423</t>
+          <t>276343</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>237973</t>
+          <t>262403</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>260989</t>
+          <t>287237</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>511904</t>
+          <t>563884</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>490587</t>
+          <t>541783</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>529944</t>
+          <t>582904</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>32610</t>
+          <t>34540</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23110</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43448</t>
+          <t>45845</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21727</t>
+          <t>24465</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37382</t>
+          <t>40539</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>61441</t>
+          <t>66325</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>50369</t>
+          <t>53753</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>76040</t>
+          <t>80343</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>343966</t>
+          <t>375160</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>343966</t>
+          <t>375160</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>343966</t>
+          <t>375160</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>332510</t>
+          <t>368453</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>332510</t>
+          <t>368453</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>332510</t>
+          <t>368453</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>676476</t>
+          <t>743613</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>676476</t>
+          <t>743613</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>676476</t>
+          <t>743613</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22653</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>23438</t>
+          <t>26289</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>38822</t>
+          <t>43770</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>47524</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>23486</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>64382</t>
+          <t>75168</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>56966</t>
+          <t>66649</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>72279</t>
+          <t>83801</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>57841</t>
+          <t>63212</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>55692</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>64972</t>
+          <t>70826</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>122223</t>
+          <t>138380</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>112465</t>
+          <t>125951</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>132717</t>
+          <t>148899</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>96618</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>96618</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>96618</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>100364</t>
+          <t>109810</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>100364</t>
+          <t>109810</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>100364</t>
+          <t>109810</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>196982</t>
+          <t>220545</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>196982</t>
+          <t>220545</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>196982</t>
+          <t>220545</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>18577</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>22224</t>
+          <t>24754</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>25776</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>31961</t>
+          <t>36385</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>16156</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>19469</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>27191</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>33598</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>23350</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>36658</t>
+          <t>42003</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>31263</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>31263</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>31263</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>52496</t>
+          <t>57456</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>52496</t>
+          <t>57456</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>52496</t>
+          <t>57456</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>83759</t>
+          <t>91860</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>83759</t>
+          <t>91860</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>83759</t>
+          <t>91860</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>456159</t>
+          <t>233320</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>224683</t>
+          <t>198641</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1024458</t>
+          <t>271654</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>211556</t>
+          <t>242703</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>184339</t>
+          <t>216045</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>240820</t>
+          <t>270603</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>667715</t>
+          <t>476023</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>427884</t>
+          <t>430494</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1330652</t>
+          <t>521633</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>29767</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>49859</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>74068</t>
+          <t>84200</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>50834</t>
+          <t>67036</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>104547</t>
+          <t>106136</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>58110</t>
+          <t>59756</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>47451</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>78916</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,27 +5795,27 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>132178</t>
+          <t>143955</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>103950</t>
+          <t>121775</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>166601</t>
+          <t>171654</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1676552</t>
+          <t>1856456</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1187141</t>
+          <t>1810686</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1884601</t>
+          <t>1898698</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1705215</t>
+          <t>1803249</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1665455</t>
+          <t>1764351</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1756033</t>
+          <t>1837126</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>3381767</t>
+          <t>3659705</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2806577</t>
+          <t>3601096</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3599820</t>
+          <t>3717623</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>165617</t>
+          <t>175029</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>116058</t>
+          <t>150217</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>201349</t>
+          <t>204818</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>178385</t>
+          <t>198524</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>152412</t>
+          <t>177864</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>203517</t>
+          <t>225848</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>344002</t>
+          <t>373553</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>284619</t>
+          <t>337173</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>390844</t>
+          <t>410293</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2378587</t>
+          <t>2362527</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2378587</t>
+          <t>2362527</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2378587</t>
+          <t>2362527</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2173061</t>
+          <t>2326121</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2173061</t>
+          <t>2326121</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2173061</t>
+          <t>2326121</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>4551648</t>
+          <t>4688648</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>4551648</t>
+          <t>4688648</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>4551648</t>
+          <t>4688648</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
